--- a/prix/motip-spray.xlsx
+++ b/prix/motip-spray.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A784311-46D7-4D81-9B05-D9E0664AF918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DEBC88-F520-4A9C-A1E5-25D2BB0E6AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -2875,7 +2875,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2889,7 +2889,7 @@
         <v>625</v>
       </c>
       <c r="D4" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>8</v>
@@ -2909,13 +2909,13 @@
         <v>626</v>
       </c>
       <c r="D5" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2929,7 +2929,7 @@
         <v>627</v>
       </c>
       <c r="D6" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>10</v>
@@ -2949,7 +2949,7 @@
         <v>628</v>
       </c>
       <c r="D7" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>11</v>
@@ -2969,7 +2969,7 @@
         <v>629</v>
       </c>
       <c r="D8" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>12</v>
@@ -2989,7 +2989,7 @@
         <v>630</v>
       </c>
       <c r="D9" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>13</v>
@@ -3009,7 +3009,7 @@
         <v>631</v>
       </c>
       <c r="D10" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>14</v>
@@ -3029,7 +3029,7 @@
         <v>632</v>
       </c>
       <c r="D11" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>15</v>
@@ -3055,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -3069,7 +3069,7 @@
         <v>634</v>
       </c>
       <c r="D13" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
@@ -3095,7 +3095,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -3109,13 +3109,13 @@
         <v>636</v>
       </c>
       <c r="D15" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -3149,13 +3149,13 @@
         <v>638</v>
       </c>
       <c r="D17" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3169,13 +3169,13 @@
         <v>639</v>
       </c>
       <c r="D18" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3189,7 +3189,7 @@
         <v>640</v>
       </c>
       <c r="D19" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
@@ -3209,7 +3209,7 @@
         <v>641</v>
       </c>
       <c r="D20" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
@@ -3229,7 +3229,7 @@
         <v>642</v>
       </c>
       <c r="D21" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
@@ -3249,13 +3249,13 @@
         <v>643</v>
       </c>
       <c r="D22" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3269,7 +3269,7 @@
         <v>644</v>
       </c>
       <c r="D23" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
@@ -3289,7 +3289,7 @@
         <v>645</v>
       </c>
       <c r="D24" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
@@ -3309,7 +3309,7 @@
         <v>646</v>
       </c>
       <c r="D25" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>29</v>
@@ -3329,13 +3329,13 @@
         <v>647</v>
       </c>
       <c r="D26" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F26" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3349,7 +3349,7 @@
         <v>648</v>
       </c>
       <c r="D27" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
@@ -3409,7 +3409,7 @@
         <v>651</v>
       </c>
       <c r="D30" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>34</v>
@@ -3449,7 +3449,7 @@
         <v>653</v>
       </c>
       <c r="D32" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>36</v>
@@ -3469,13 +3469,13 @@
         <v>654</v>
       </c>
       <c r="D33" s="13">
-        <v>9.99</v>
+        <v>10.5</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F33" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3509,7 +3509,7 @@
         <v>656</v>
       </c>
       <c r="D35" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>39</v>
@@ -3529,7 +3529,7 @@
         <v>657</v>
       </c>
       <c r="D36" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>40</v>
@@ -3549,7 +3549,7 @@
         <v>658</v>
       </c>
       <c r="D37" s="13">
-        <v>9.66</v>
+        <v>10.5</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>41</v>
@@ -3569,7 +3569,7 @@
         <v>569</v>
       </c>
       <c r="D38" s="13">
-        <v>10.5</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>42</v>
@@ -3589,7 +3589,7 @@
         <v>659</v>
       </c>
       <c r="D39" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>43</v>
@@ -3609,7 +3609,7 @@
         <v>660</v>
       </c>
       <c r="D40" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>44</v>
@@ -3629,7 +3629,7 @@
         <v>661</v>
       </c>
       <c r="D41" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>45</v>
@@ -3649,7 +3649,7 @@
         <v>662</v>
       </c>
       <c r="D42" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>46</v>
@@ -3675,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="F43" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3689,7 +3689,7 @@
         <v>664</v>
       </c>
       <c r="D44" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>48</v>
@@ -3709,7 +3709,7 @@
         <v>665</v>
       </c>
       <c r="D45" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>49</v>
@@ -3729,7 +3729,7 @@
         <v>666</v>
       </c>
       <c r="D46" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>50</v>
@@ -3749,7 +3749,7 @@
         <v>667</v>
       </c>
       <c r="D47" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>51</v>
@@ -3769,7 +3769,7 @@
         <v>668</v>
       </c>
       <c r="D48" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>52</v>
@@ -3789,13 +3789,13 @@
         <v>666</v>
       </c>
       <c r="D49" s="13">
-        <v>17.04</v>
+        <v>19.650000000000002</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F49" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3809,13 +3809,13 @@
         <v>667</v>
       </c>
       <c r="D50" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>54</v>
       </c>
       <c r="F50" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3849,7 +3849,7 @@
         <v>670</v>
       </c>
       <c r="D52" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>56</v>
@@ -3869,13 +3869,13 @@
         <v>663</v>
       </c>
       <c r="D53" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>57</v>
       </c>
       <c r="F53" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -3889,7 +3889,7 @@
         <v>671</v>
       </c>
       <c r="D54" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>58</v>
@@ -3909,7 +3909,7 @@
         <v>672</v>
       </c>
       <c r="D55" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>59</v>
@@ -3929,7 +3929,7 @@
         <v>673</v>
       </c>
       <c r="D56" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>60</v>
@@ -3949,7 +3949,7 @@
         <v>674</v>
       </c>
       <c r="D57" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>61</v>
@@ -3969,7 +3969,7 @@
         <v>675</v>
       </c>
       <c r="D58" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>62</v>
@@ -3989,7 +3989,7 @@
         <v>676</v>
       </c>
       <c r="D59" s="13">
-        <v>17.900000000000002</v>
+        <v>17.88</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>63</v>
@@ -4029,7 +4029,7 @@
         <v>677</v>
       </c>
       <c r="D61" s="13">
-        <v>17.04</v>
+        <v>17.88</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>65</v>
@@ -4069,7 +4069,7 @@
         <v>679</v>
       </c>
       <c r="D63" s="13">
-        <v>16.47</v>
+        <v>17.88</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>67</v>
@@ -4089,13 +4089,13 @@
         <v>680</v>
       </c>
       <c r="D64" s="13">
-        <v>17.04</v>
+        <v>19.650000000000002</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>68</v>
       </c>
       <c r="F64" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -4109,7 +4109,7 @@
         <v>681</v>
       </c>
       <c r="D65" s="13">
-        <v>16.47</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>69</v>
@@ -4129,7 +4129,7 @@
         <v>682</v>
       </c>
       <c r="D66" s="13">
-        <v>17</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>70</v>
@@ -4169,13 +4169,13 @@
         <v>684</v>
       </c>
       <c r="D68" s="13">
-        <v>17.900000000000002</v>
+        <v>19.650000000000002</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>72</v>
       </c>
       <c r="F68" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4189,7 +4189,7 @@
         <v>685</v>
       </c>
       <c r="D69" s="13">
-        <v>17.04</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>73</v>
@@ -4209,7 +4209,7 @@
         <v>686</v>
       </c>
       <c r="D70" s="13">
-        <v>16.47</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>74</v>
@@ -4229,7 +4229,7 @@
         <v>687</v>
       </c>
       <c r="D71" s="13">
-        <v>17.04</v>
+        <v>17.900000000000002</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>75</v>
@@ -4289,13 +4289,13 @@
         <v>690</v>
       </c>
       <c r="D74" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F74" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -4309,7 +4309,7 @@
         <v>691</v>
       </c>
       <c r="D75" s="13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>79</v>
@@ -4349,7 +4349,7 @@
         <v>692</v>
       </c>
       <c r="D77" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>81</v>
@@ -4375,7 +4375,7 @@
         <v>82</v>
       </c>
       <c r="F78" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -4389,7 +4389,7 @@
         <v>694</v>
       </c>
       <c r="D79" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>83</v>
@@ -4409,13 +4409,13 @@
         <v>695</v>
       </c>
       <c r="D80" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>84</v>
       </c>
       <c r="F80" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -4429,7 +4429,7 @@
         <v>696</v>
       </c>
       <c r="D81" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>85</v>
@@ -4449,13 +4449,13 @@
         <v>697</v>
       </c>
       <c r="D82" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>86</v>
       </c>
       <c r="F82" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -4469,7 +4469,7 @@
         <v>698</v>
       </c>
       <c r="D83" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>87</v>
@@ -4489,7 +4489,7 @@
         <v>699</v>
       </c>
       <c r="D84" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>88</v>
@@ -4509,7 +4509,7 @@
         <v>700</v>
       </c>
       <c r="D85" s="13">
-        <v>10.5</v>
+        <v>13.75</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>89</v>
@@ -4529,7 +4529,7 @@
         <v>701</v>
       </c>
       <c r="D86" s="13">
-        <v>10.5</v>
+        <v>13.75</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>90</v>
@@ -4549,7 +4549,7 @@
         <v>702</v>
       </c>
       <c r="D87" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>91</v>
@@ -4569,7 +4569,7 @@
         <v>703</v>
       </c>
       <c r="D88" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>92</v>
@@ -4589,13 +4589,13 @@
         <v>704</v>
       </c>
       <c r="D89" s="13">
-        <v>10.5</v>
+        <v>13.75</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>93</v>
       </c>
       <c r="F89" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -4609,7 +4609,7 @@
         <v>705</v>
       </c>
       <c r="D90" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>94</v>
@@ -4629,7 +4629,7 @@
         <v>704</v>
       </c>
       <c r="D91" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>95</v>
@@ -4649,7 +4649,7 @@
         <v>706</v>
       </c>
       <c r="D92" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>96</v>
@@ -4669,7 +4669,7 @@
         <v>707</v>
       </c>
       <c r="D93" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>97</v>
@@ -4689,7 +4689,7 @@
         <v>708</v>
       </c>
       <c r="D94" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>98</v>
@@ -4709,7 +4709,7 @@
         <v>709</v>
       </c>
       <c r="D95" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>99</v>
@@ -4729,7 +4729,7 @@
         <v>703</v>
       </c>
       <c r="D96" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>100</v>
@@ -4749,7 +4749,7 @@
         <v>704</v>
       </c>
       <c r="D97" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>101</v>
@@ -4769,13 +4769,13 @@
         <v>710</v>
       </c>
       <c r="D98" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>102</v>
       </c>
       <c r="F98" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -4789,7 +4789,7 @@
         <v>711</v>
       </c>
       <c r="D99" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>103</v>
@@ -4809,7 +4809,7 @@
         <v>712</v>
       </c>
       <c r="D100" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>104</v>
@@ -4829,7 +4829,7 @@
         <v>703</v>
       </c>
       <c r="D101" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>105</v>
@@ -4869,7 +4869,7 @@
         <v>713</v>
       </c>
       <c r="D103" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>107</v>
@@ -4889,7 +4889,7 @@
         <v>698</v>
       </c>
       <c r="D104" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>108</v>
@@ -4909,7 +4909,7 @@
         <v>714</v>
       </c>
       <c r="D105" s="13">
-        <v>10.47</v>
+        <v>13.75</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>109</v>
@@ -4929,13 +4929,13 @@
         <v>710</v>
       </c>
       <c r="D106" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>110</v>
       </c>
       <c r="F106" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -4949,7 +4949,7 @@
         <v>715</v>
       </c>
       <c r="D107" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>111</v>
@@ -4969,7 +4969,7 @@
         <v>706</v>
       </c>
       <c r="D108" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>112</v>
@@ -4989,7 +4989,7 @@
         <v>696</v>
       </c>
       <c r="D109" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>113</v>
@@ -5009,7 +5009,7 @@
         <v>707</v>
       </c>
       <c r="D110" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>114</v>
@@ -5029,13 +5029,13 @@
         <v>698</v>
       </c>
       <c r="D111" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>115</v>
       </c>
       <c r="F111" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -5055,7 +5055,7 @@
         <v>116</v>
       </c>
       <c r="F112" s="14">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -5069,13 +5069,13 @@
         <v>717</v>
       </c>
       <c r="D113" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>117</v>
       </c>
       <c r="F113" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -5089,7 +5089,7 @@
         <v>718</v>
       </c>
       <c r="D114" s="13">
-        <v>13.08</v>
+        <v>13.75</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>118</v>
@@ -5109,7 +5109,7 @@
         <v>719</v>
       </c>
       <c r="D115" s="13">
-        <v>13.08</v>
+        <v>13.75</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>119</v>
@@ -5135,7 +5135,7 @@
         <v>120</v>
       </c>
       <c r="F116" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -5149,13 +5149,13 @@
         <v>721</v>
       </c>
       <c r="D117" s="13">
-        <v>13.75</v>
+        <v>15.1</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>121</v>
       </c>
       <c r="F117" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -5169,7 +5169,7 @@
         <v>569</v>
       </c>
       <c r="D118" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>122</v>
@@ -5189,7 +5189,7 @@
         <v>569</v>
       </c>
       <c r="D119" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>123</v>
@@ -5209,7 +5209,7 @@
         <v>569</v>
       </c>
       <c r="D120" s="13">
-        <v>13.1</v>
+        <v>13.75</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>124</v>
@@ -5229,13 +5229,13 @@
         <v>569</v>
       </c>
       <c r="D121" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>125</v>
       </c>
       <c r="F121" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -5249,7 +5249,7 @@
         <v>569</v>
       </c>
       <c r="D122" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>126</v>
@@ -5269,7 +5269,7 @@
         <v>569</v>
       </c>
       <c r="D123" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>127</v>
@@ -5289,7 +5289,7 @@
         <v>569</v>
       </c>
       <c r="D124" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>128</v>
@@ -5329,7 +5329,7 @@
         <v>569</v>
       </c>
       <c r="D126" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>130</v>
@@ -5369,7 +5369,7 @@
         <v>569</v>
       </c>
       <c r="D128" s="13">
-        <v>12.64</v>
+        <v>13.75</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>132</v>
@@ -5389,7 +5389,7 @@
         <v>628</v>
       </c>
       <c r="D129" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>133</v>
@@ -5409,7 +5409,7 @@
         <v>722</v>
       </c>
       <c r="D130" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>134</v>
@@ -5429,13 +5429,13 @@
         <v>723</v>
       </c>
       <c r="D131" s="13">
-        <v>18.350000000000001</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>135</v>
       </c>
       <c r="F131" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -5449,7 +5449,7 @@
         <v>724</v>
       </c>
       <c r="D132" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>136</v>
@@ -5469,7 +5469,7 @@
         <v>725</v>
       </c>
       <c r="D133" s="13">
-        <v>18.350000000000001</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>137</v>
@@ -5489,7 +5489,7 @@
         <v>627</v>
       </c>
       <c r="D134" s="13">
-        <v>13.9</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>138</v>
@@ -5509,7 +5509,7 @@
         <v>726</v>
       </c>
       <c r="D135" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>139</v>
@@ -5529,7 +5529,7 @@
         <v>727</v>
       </c>
       <c r="D136" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>140</v>
@@ -5549,7 +5549,7 @@
         <v>626</v>
       </c>
       <c r="D137" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>141</v>
@@ -5569,7 +5569,7 @@
         <v>625</v>
       </c>
       <c r="D138" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>142</v>
@@ -5589,7 +5589,7 @@
         <v>631</v>
       </c>
       <c r="D139" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>143</v>
@@ -5609,7 +5609,7 @@
         <v>630</v>
       </c>
       <c r="D140" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>144</v>
@@ -5629,7 +5629,7 @@
         <v>728</v>
       </c>
       <c r="D141" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>145</v>
@@ -5649,7 +5649,7 @@
         <v>729</v>
       </c>
       <c r="D142" s="13">
-        <v>18.37</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E142" s="9" t="s">
         <v>146</v>
@@ -5669,7 +5669,7 @@
         <v>730</v>
       </c>
       <c r="D143" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>147</v>
@@ -5689,7 +5689,7 @@
         <v>633</v>
       </c>
       <c r="D144" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>148</v>
@@ -5709,7 +5709,7 @@
         <v>731</v>
       </c>
       <c r="D145" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>149</v>
@@ -5729,7 +5729,7 @@
         <v>635</v>
       </c>
       <c r="D146" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>150</v>
@@ -5749,7 +5749,7 @@
         <v>634</v>
       </c>
       <c r="D147" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>151</v>
@@ -5769,7 +5769,7 @@
         <v>636</v>
       </c>
       <c r="D148" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>152</v>
@@ -5789,7 +5789,7 @@
         <v>637</v>
       </c>
       <c r="D149" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>153</v>
@@ -5809,7 +5809,7 @@
         <v>732</v>
       </c>
       <c r="D150" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E150" s="9" t="s">
         <v>154</v>
@@ -5829,7 +5829,7 @@
         <v>640</v>
       </c>
       <c r="D151" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>155</v>
@@ -5849,7 +5849,7 @@
         <v>641</v>
       </c>
       <c r="D152" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E152" s="9" t="s">
         <v>156</v>
@@ -5869,7 +5869,7 @@
         <v>733</v>
       </c>
       <c r="D153" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>157</v>
@@ -5889,7 +5889,7 @@
         <v>734</v>
       </c>
       <c r="D154" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E154" s="9" t="s">
         <v>158</v>
@@ -5909,7 +5909,7 @@
         <v>642</v>
       </c>
       <c r="D155" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>159</v>
@@ -5929,7 +5929,7 @@
         <v>735</v>
       </c>
       <c r="D156" s="13">
-        <v>18.37</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E156" s="9" t="s">
         <v>160</v>
@@ -5949,7 +5949,7 @@
         <v>736</v>
       </c>
       <c r="D157" s="13">
-        <v>18.66</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>161</v>
@@ -5969,7 +5969,7 @@
         <v>737</v>
       </c>
       <c r="D158" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>162</v>
@@ -5989,7 +5989,7 @@
         <v>643</v>
       </c>
       <c r="D159" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>163</v>
@@ -6009,7 +6009,7 @@
         <v>738</v>
       </c>
       <c r="D160" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E160" s="9" t="s">
         <v>164</v>
@@ -6029,7 +6029,7 @@
         <v>739</v>
       </c>
       <c r="D161" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>165</v>
@@ -6049,7 +6049,7 @@
         <v>740</v>
       </c>
       <c r="D162" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E162" s="9" t="s">
         <v>166</v>
@@ -6069,7 +6069,7 @@
         <v>741</v>
       </c>
       <c r="D163" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>167</v>
@@ -6089,7 +6089,7 @@
         <v>645</v>
       </c>
       <c r="D164" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>168</v>
@@ -6109,7 +6109,7 @@
         <v>646</v>
       </c>
       <c r="D165" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>169</v>
@@ -6129,7 +6129,7 @@
         <v>742</v>
       </c>
       <c r="D166" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>170</v>
@@ -6149,7 +6149,7 @@
         <v>743</v>
       </c>
       <c r="D167" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>171</v>
@@ -6169,7 +6169,7 @@
         <v>744</v>
       </c>
       <c r="D168" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E168" s="9" t="s">
         <v>172</v>
@@ -6189,7 +6189,7 @@
         <v>647</v>
       </c>
       <c r="D169" s="13">
-        <v>18.37</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>173</v>
@@ -6209,7 +6209,7 @@
         <v>745</v>
       </c>
       <c r="D170" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E170" s="9" t="s">
         <v>174</v>
@@ -6229,7 +6229,7 @@
         <v>648</v>
       </c>
       <c r="D171" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>175</v>
@@ -6249,7 +6249,7 @@
         <v>649</v>
       </c>
       <c r="D172" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E172" s="9" t="s">
         <v>176</v>
@@ -6269,7 +6269,7 @@
         <v>746</v>
       </c>
       <c r="D173" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>177</v>
@@ -6289,7 +6289,7 @@
         <v>747</v>
       </c>
       <c r="D174" s="13">
-        <v>17.48</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>178</v>
@@ -6309,7 +6309,7 @@
         <v>748</v>
       </c>
       <c r="D175" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>179</v>
@@ -6329,7 +6329,7 @@
         <v>749</v>
       </c>
       <c r="D176" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E176" s="9" t="s">
         <v>180</v>
@@ -6349,7 +6349,7 @@
         <v>750</v>
       </c>
       <c r="D177" s="13">
-        <v>18.38</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>181</v>
@@ -6369,7 +6369,7 @@
         <v>751</v>
       </c>
       <c r="D178" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E178" s="9" t="s">
         <v>182</v>
@@ -6389,7 +6389,7 @@
         <v>752</v>
       </c>
       <c r="D179" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>183</v>
@@ -6409,13 +6409,13 @@
         <v>753</v>
       </c>
       <c r="D180" s="13">
-        <v>18.38</v>
+        <v>20.5</v>
       </c>
       <c r="E180" s="9" t="s">
         <v>184</v>
       </c>
       <c r="F180" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -6429,7 +6429,7 @@
         <v>754</v>
       </c>
       <c r="D181" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>185</v>
@@ -6449,7 +6449,7 @@
         <v>755</v>
       </c>
       <c r="D182" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E182" s="9" t="s">
         <v>186</v>
@@ -6469,7 +6469,7 @@
         <v>756</v>
       </c>
       <c r="D183" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>187</v>
@@ -6489,7 +6489,7 @@
         <v>650</v>
       </c>
       <c r="D184" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E184" s="9" t="s">
         <v>188</v>
@@ -6509,7 +6509,7 @@
         <v>757</v>
       </c>
       <c r="D185" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>189</v>
@@ -6529,7 +6529,7 @@
         <v>758</v>
       </c>
       <c r="D186" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E186" s="9" t="s">
         <v>190</v>
@@ -6549,13 +6549,13 @@
         <v>759</v>
       </c>
       <c r="D187" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>191</v>
       </c>
       <c r="F187" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -6569,7 +6569,7 @@
         <v>760</v>
       </c>
       <c r="D188" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E188" s="9" t="s">
         <v>192</v>
@@ -6589,7 +6589,7 @@
         <v>761</v>
       </c>
       <c r="D189" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>193</v>
@@ -6609,7 +6609,7 @@
         <v>762</v>
       </c>
       <c r="D190" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E190" s="9" t="s">
         <v>194</v>
@@ -6629,13 +6629,13 @@
         <v>763</v>
       </c>
       <c r="D191" s="13">
-        <v>17.48</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>195</v>
       </c>
       <c r="F191" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -6649,7 +6649,7 @@
         <v>764</v>
       </c>
       <c r="D192" s="13">
-        <v>18.38</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E192" s="9" t="s">
         <v>196</v>
@@ -6669,7 +6669,7 @@
         <v>653</v>
       </c>
       <c r="D193" s="13">
-        <v>17.5</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>197</v>
@@ -6689,7 +6689,7 @@
         <v>765</v>
       </c>
       <c r="D194" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E194" s="9" t="s">
         <v>198</v>
@@ -6709,7 +6709,7 @@
         <v>766</v>
       </c>
       <c r="D195" s="13">
-        <v>17.48</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>199</v>
@@ -6729,13 +6729,13 @@
         <v>654</v>
       </c>
       <c r="D196" s="13">
-        <v>17.48</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E196" s="9" t="s">
         <v>200</v>
       </c>
       <c r="F196" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -6749,13 +6749,13 @@
         <v>655</v>
       </c>
       <c r="D197" s="13">
-        <v>18.38</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>201</v>
       </c>
       <c r="F197" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -6769,7 +6769,7 @@
         <v>767</v>
       </c>
       <c r="D198" s="13">
-        <v>18.670000000000002</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E198" s="9" t="s">
         <v>202</v>
@@ -6789,7 +6789,7 @@
         <v>656</v>
       </c>
       <c r="D199" s="13">
-        <v>18.670000000000002</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>203</v>
@@ -6809,7 +6809,7 @@
         <v>768</v>
       </c>
       <c r="D200" s="13">
-        <v>18.37</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>204</v>
@@ -6829,7 +6829,7 @@
         <v>657</v>
       </c>
       <c r="D201" s="13">
-        <v>18.37</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>205</v>
@@ -7044,7 +7044,7 @@
         <v>499</v>
       </c>
       <c r="D215" s="13">
-        <v>13.620000000000001</v>
+        <v>15.21</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>219</v>
@@ -7059,13 +7059,13 @@
         <v>500</v>
       </c>
       <c r="D216" s="13">
-        <v>12.09</v>
+        <v>13.3</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>220</v>
       </c>
       <c r="F216" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -7074,13 +7074,13 @@
         <v>501</v>
       </c>
       <c r="D217" s="13">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>221</v>
       </c>
       <c r="F217" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -7104,13 +7104,13 @@
         <v>503</v>
       </c>
       <c r="D219" s="13">
-        <v>12.09</v>
+        <v>13.3</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>223</v>
       </c>
       <c r="F219" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -7119,7 +7119,7 @@
         <v>504</v>
       </c>
       <c r="D220" s="13">
-        <v>12.34</v>
+        <v>15.21</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>224</v>
@@ -7134,7 +7134,7 @@
         <v>505</v>
       </c>
       <c r="D221" s="13">
-        <v>12.34</v>
+        <v>15.21</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>225</v>
@@ -7149,13 +7149,13 @@
         <v>506</v>
       </c>
       <c r="D222" s="13">
-        <v>12.780000000000001</v>
+        <v>15.21</v>
       </c>
       <c r="E222" s="9" t="s">
         <v>226</v>
       </c>
       <c r="F222" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
@@ -7164,13 +7164,13 @@
         <v>507</v>
       </c>
       <c r="D223" s="13">
-        <v>13.620000000000001</v>
+        <v>15</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>227</v>
       </c>
       <c r="F223" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -7209,7 +7209,7 @@
         <v>510</v>
       </c>
       <c r="D226" s="13">
-        <v>12.09</v>
+        <v>15.21</v>
       </c>
       <c r="E226" s="9" t="s">
         <v>230</v>
@@ -7239,13 +7239,13 @@
         <v>512</v>
       </c>
       <c r="D228" s="13">
-        <v>10.9</v>
+        <v>13.3</v>
       </c>
       <c r="E228" s="9" t="s">
         <v>232</v>
       </c>
       <c r="F228" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -7740,7 +7740,7 @@
         <v>265</v>
       </c>
       <c r="F261" s="14">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -7770,7 +7770,7 @@
         <v>267</v>
       </c>
       <c r="F263" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -8009,13 +8009,13 @@
         <v>769</v>
       </c>
       <c r="D279" s="13">
-        <v>18.38</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>283</v>
       </c>
       <c r="F279" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
@@ -8029,7 +8029,7 @@
         <v>770</v>
       </c>
       <c r="D280" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E280" s="9" t="s">
         <v>284</v>
@@ -8049,7 +8049,7 @@
         <v>771</v>
       </c>
       <c r="D281" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>285</v>
@@ -8069,7 +8069,7 @@
         <v>772</v>
       </c>
       <c r="D282" s="13">
-        <v>18.38</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E282" s="9" t="s">
         <v>286</v>
@@ -8089,7 +8089,7 @@
         <v>773</v>
       </c>
       <c r="D283" s="13">
-        <v>16.899999999999999</v>
+        <v>18.650000000000002</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>287</v>
